--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486971_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486971_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. JUANOLA MADERA</t>
+          <t>F. GARRIDO TEBAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6925</v>
+        <v>6.3097</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4458</v>
+        <v>4.0002</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2467</v>
+        <v>2.3095</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7332</v>
+        <v>4.7657</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7041</v>
+        <v>1.0214</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9709</v>
+        <v>3.7443</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2321</v>
+        <v>3.578</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4168</v>
+        <v>0.4866</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.1847</v>
+        <v>3.0914</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5011</v>
+        <v>1.1877</v>
       </c>
       <c r="N2" t="n">
-        <v>1.2873</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7863</v>
+        <v>0.6529</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2053</v>
+        <v>1.0267</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2588</v>
+        <v>-0.4107</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0534</v>
+        <v>1.4374</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3967</v>
+        <v>0.5173</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8749</v>
+        <v>0.8329</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4782</v>
+        <v>-0.3155</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7679</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5975</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. GARRIDO TEBAN</t>
+          <t>J. JUANOLA MADERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1114</v>
+        <v>5.6571</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8611</v>
+        <v>4.5586</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2503</v>
+        <v>1.0985</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7657</v>
+        <v>3.7332</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0214</v>
+        <v>4.7041</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7443</v>
+        <v>-0.9709</v>
       </c>
       <c r="J3" t="n">
-        <v>3.578</v>
+        <v>3.2321</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4866</v>
+        <v>3.4168</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0914</v>
+        <v>-0.1847</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1877</v>
+        <v>0.5011</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5348000000000001</v>
+        <v>1.2873</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6529</v>
+        <v>-0.7863</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4107</v>
+        <v>-2.2588</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4374</v>
+        <v>2.0534</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.681</v>
+        <v>0.3614</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3062</v>
+        <v>0.9878</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3748</v>
+        <v>-0.6264</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.7679</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.5975</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1942</v>
+        <v>4.0985</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2406</v>
+        <v>3.2634</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9536</v>
+        <v>0.8351</v>
       </c>
       <c r="G4" t="n">
         <v>3.6865</v>
@@ -766,13 +766,13 @@
         <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.447</v>
+        <v>0.4572</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0699</v>
+        <v>0.9529</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3771</v>
+        <v>-0.4957</v>
       </c>
       <c r="V4" t="n">
         <v>2.0082</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2783</v>
+        <v>-0.5214</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6739</v>
+        <v>1.2826</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9522</v>
+        <v>-1.804</v>
       </c>
       <c r="G5" t="n">
         <v>0.0107</v>
@@ -844,13 +844,13 @@
         <v>0.8214</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0098</v>
+        <v>-0.2528</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.5578</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9588</v>
+        <v>-0.8106</v>
       </c>
       <c r="V5" t="n">
         <v>0.1314</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4545</v>
+        <v>-0.873</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9644</v>
+        <v>-2.4719</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5099</v>
+        <v>1.5988</v>
       </c>
       <c r="G6" t="n">
         <v>1.0902</v>
@@ -922,13 +922,13 @@
         <v>2.2588</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7489</v>
+        <v>0.3304</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6773</v>
+        <v>1.1698</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9284</v>
+        <v>-0.8395</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2402</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. COLL COMABELLA</t>
+          <t>G. MARTINEZ RIVERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7516</v>
+        <v>-1.6491</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1734</v>
+        <v>-3.0826</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4218</v>
+        <v>1.4335</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.425</v>
+        <v>-3.1725</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2856</v>
+        <v>-1.0544</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1395</v>
+        <v>-2.1181</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-3.7893</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0195</v>
+        <v>-2.3417</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6974</v>
+        <v>-1.4476</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2528</v>
+        <v>0.6168</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.305</v>
+        <v>1.2873</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5579</v>
+        <v>-0.6706</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.0267</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2321</v>
+        <v>-2.2588</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2053</v>
+        <v>1.4374</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2998</v>
+        <v>-0.0125</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2635</v>
+        <v>0.3679</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0364</v>
+        <v>-0.3804</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.3573</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.5975</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. MARTINEZ RIVERA</t>
+          <t>N. FERRER IGLESIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0848</v>
+        <v>-1.7139</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.7258</v>
+        <v>-0.1424</v>
       </c>
       <c r="F8" t="n">
-        <v>1.641</v>
+        <v>-1.5715</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.1725</v>
+        <v>0.1707</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0544</v>
+        <v>0.5286</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1181</v>
+        <v>-0.3579</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.7893</v>
+        <v>0.0359</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.3417</v>
+        <v>0.7202</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4476</v>
+        <v>-0.6843</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6168</v>
+        <v>0.1348</v>
       </c>
       <c r="N8" t="n">
-        <v>1.2873</v>
+        <v>-0.1917</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6706</v>
+        <v>0.3264</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2588</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4482</v>
+        <v>-0.7594</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2753</v>
+        <v>-0.1783</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1729</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>2.3573</v>
+        <v>-2.3573</v>
       </c>
       <c r="W8" t="n">
-        <v>2.5975</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2402</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. FERRER IGLESIA</t>
+          <t>E. COLL COMABELLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1602</v>
+        <v>-1.8043</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3516</v>
+        <v>-2.1076</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8086</v>
+        <v>0.3033</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1707</v>
+        <v>-0.425</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5286</v>
+        <v>-0.2856</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3579</v>
+        <v>-0.1395</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0359</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7202</v>
+        <v>0.0195</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6843</v>
+        <v>-0.6974</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1348</v>
+        <v>0.2528</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1917</v>
+        <v>-0.305</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3264</v>
+        <v>0.5579</v>
       </c>
       <c r="P9" t="n">
-        <v>1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2321</v>
+        <v>0.2053</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2057</v>
+        <v>-0.3525</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3875</v>
+        <v>-0.1976</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8182</v>
+        <v>-0.1549</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.974</v>
+        <v>-2.3876</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.917</v>
+        <v>-0.301</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.057</v>
+        <v>-2.0866</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7911</v>
@@ -1234,13 +1234,13 @@
         <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9961</v>
+        <v>-0.4097</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0541</v>
+        <v>0.6701</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0501</v>
+        <v>-1.0798</v>
       </c>
       <c r="V10" t="n">
         <v>-2.0082</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1666</v>
+        <v>-4.0118</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8895</v>
+        <v>-1.8237</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2771</v>
+        <v>-2.1881</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4242</v>
@@ -1312,13 +1312,13 @@
         <v>0.4107</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8861</v>
+        <v>-0.7313</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6587</v>
+        <v>-0.5928</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2274</v>
+        <v>-0.1385</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2402</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.128099999999999</v>
+        <v>3.104199999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1.199700000000002</v>
+        <v>3.175600000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.07159999999999966</v>
+        <v>-0.07149999999999901</v>
       </c>
       <c r="G12" t="n">
         <v>6.644200000000001</v>
@@ -1375,7 +1375,7 @@
         <v>2.4819</v>
       </c>
       <c r="N12" t="n">
-        <v>5.478400000000001</v>
+        <v>5.4784</v>
       </c>
       <c r="O12" t="n">
         <v>-2.9967</v>
@@ -1390,13 +1390,13 @@
         <v>12.3206</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.8281</v>
+        <v>-0.8518999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5943</v>
+        <v>4.570499999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.422300000000001</v>
+        <v>-5.422399999999999</v>
       </c>
       <c r="V12" t="n">
         <v>1.4189</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. TOLEDO ZAMORA</t>
+          <t>A. DUVAL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.9973</v>
+        <v>5.5416</v>
       </c>
       <c r="E13" t="n">
-        <v>5.2788</v>
+        <v>4.3645</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7186</v>
+        <v>1.1771</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3909</v>
+        <v>2.534</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2384</v>
+        <v>-1.0122</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1525</v>
+        <v>3.5462</v>
       </c>
       <c r="J13" t="n">
-        <v>2.237</v>
+        <v>3.5464</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3427</v>
+        <v>-0.347</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1057</v>
+        <v>3.8933</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1539</v>
+        <v>-1.0124</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1044</v>
+        <v>-0.6653</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2582</v>
+        <v>-0.3472</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0.8214</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6065</v>
+        <v>0.8988</v>
       </c>
       <c r="T13" t="n">
-        <v>3.9166</v>
+        <v>0.6662</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3101</v>
+        <v>0.2326</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.2875</v>
       </c>
       <c r="W13" t="n">
         <v>1.1786</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1786</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. DUVAL</t>
+          <t>C. TOLEDO ZAMORA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7509</v>
+        <v>4.294</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5738</v>
+        <v>3.1867</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1771</v>
+        <v>1.1073</v>
       </c>
       <c r="G14" t="n">
-        <v>2.534</v>
+        <v>2.3909</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.0122</v>
+        <v>2.2384</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5462</v>
+        <v>0.1525</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5464</v>
+        <v>2.237</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.347</v>
+        <v>2.3427</v>
       </c>
       <c r="L14" t="n">
-        <v>3.8933</v>
+        <v>-0.1057</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0124</v>
+        <v>0.1539</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6653</v>
+        <v>-0.1044</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3472</v>
+        <v>0.2582</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8214</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8481</v>
+        <v>2.0534</v>
       </c>
       <c r="S14" t="n">
-        <v>1.108</v>
+        <v>1.9032</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8754999999999999</v>
+        <v>1.8245</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2326</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2875</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>1.1786</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1088</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4786</v>
+        <v>2.3137</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4017</v>
+        <v>-0.1925</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8802</v>
+        <v>2.5061</v>
       </c>
       <c r="G15" t="n">
         <v>-0.8147</v>
@@ -1624,13 +1624,13 @@
         <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5281</v>
+        <v>0.307</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4221</v>
+        <v>0.6313</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9502</v>
+        <v>-0.3243</v>
       </c>
       <c r="V15" t="n">
         <v>1.1786</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8872</v>
+        <v>1.6874</v>
       </c>
       <c r="E16" t="n">
-        <v>1.95</v>
+        <v>2.2638</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0628</v>
+        <v>-0.5764</v>
       </c>
       <c r="G16" t="n">
         <v>0.435</v>
@@ -1702,13 +1702,13 @@
         <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0201</v>
+        <v>-0.2199</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.248</v>
+        <v>0.0658</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7721</v>
+        <v>-0.2857</v>
       </c>
       <c r="V16" t="n">
         <v>0.2402</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8748</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4392</v>
+        <v>1.6024</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5644</v>
+        <v>-1.5941</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1583</v>
@@ -1780,13 +1780,13 @@
         <v>1.8481</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8011</v>
+        <v>0.9346</v>
       </c>
       <c r="T17" t="n">
-        <v>1.317</v>
+        <v>0.4802</v>
       </c>
       <c r="U17" t="n">
-        <v>0.484</v>
+        <v>0.4544</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5893</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0039</v>
+        <v>-0.0101</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3859</v>
+        <v>-0.2813</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3898</v>
+        <v>0.2712</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2464</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2503</v>
+        <v>0.2363</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.1046</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2503</v>
+        <v>0.1317</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6786</v>
+        <v>-0.5821</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.7517</v>
+        <v>-2.7057</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0731</v>
+        <v>2.1236</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8643</v>
@@ -1936,13 +1936,13 @@
         <v>2.0534</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6172</v>
+        <v>0.4794</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4806</v>
+        <v>0.5654</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1365</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>0.8295</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8918</v>
+        <v>-1.8145</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6885</v>
+        <v>-1.8517</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2033</v>
+        <v>0.0372</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7858000000000001</v>
@@ -2014,13 +2014,13 @@
         <v>1.4374</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2498</v>
+        <v>-0.1724</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5851</v>
+        <v>0.2517</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6647</v>
+        <v>-0.4241</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2402</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1147</v>
+        <v>-2.7696</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.15</v>
+        <v>-2.627</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0353</v>
+        <v>-0.1426</v>
       </c>
       <c r="G21" t="n">
         <v>-3.9563</v>
@@ -2092,13 +2092,13 @@
         <v>2.2588</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4788</v>
+        <v>-0.1337</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7518</v>
+        <v>-0.2288</v>
       </c>
       <c r="U21" t="n">
-        <v>0.273</v>
+        <v>0.0951</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9384</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1108</v>
+        <v>-3.7237</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1237</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.2345</v>
+        <v>-3.6382</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7902</v>
@@ -2170,13 +2170,13 @@
         <v>1.0267</v>
       </c>
       <c r="S22" t="n">
-        <v>0.626</v>
+        <v>1.0131</v>
       </c>
       <c r="T22" t="n">
-        <v>1.4179</v>
+        <v>1.2087</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7919</v>
+        <v>-0.1956</v>
       </c>
       <c r="V22" t="n">
         <v>-2.9466</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3248</v>
+        <v>-3.9813</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9162</v>
+        <v>-3.6024</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4086</v>
+        <v>-0.379</v>
       </c>
       <c r="G23" t="n">
         <v>-2.388</v>
@@ -2248,13 +2248,13 @@
         <v>1.0267</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-0.3264</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4611</v>
+        <v>-0.1473</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2088</v>
+        <v>-0.1791</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2402</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.128</v>
+        <v>0.9638000000000009</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07150000000000034</v>
+        <v>0.07129999999999903</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.199499999999999</v>
+        <v>0.8921999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-6.644100000000001</v>
@@ -2326,13 +2326,13 @@
         <v>16.4274</v>
       </c>
       <c r="S24" t="n">
-        <v>2.828</v>
+        <v>4.92</v>
       </c>
       <c r="T24" t="n">
-        <v>5.422499999999999</v>
+        <v>5.4223</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.5944</v>
+        <v>-0.5022999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4189</v>
